--- a/final_runs/Sensitivity_analysis_simple/sensitivity_data.xlsx
+++ b/final_runs/Sensitivity_analysis_simple/sensitivity_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
   <si>
     <t>Experiment</t>
   </si>
@@ -37,21 +37,12 @@
     <t>F1 CI High</t>
   </si>
   <si>
-    <t>F1 Min</t>
-  </si>
-  <si>
-    <t>F1 Max</t>
-  </si>
-  <si>
     <t>ΔF1</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>F1 Values</t>
-  </si>
-  <si>
     <t>Corr. Citation</t>
   </si>
   <si>
@@ -73,49 +64,7 @@
     <t>Mechanistic</t>
   </si>
   <si>
-    <t>Mechanistic-Lit</t>
-  </si>
-  <si>
-    <t>[0.4528301886792453, 0.45627376425855515, 0.45454545454545453, 0.36430678466076694, 0.36565507031828276, 0.36363636363636365, 0.4094488188976378, 0.416, 0.416]</t>
-  </si>
-  <si>
-    <t>[0.45454545454545453, 0.4528301886792453, 0.45454545454545453, 0.3630952380952381, 0.3707533234859675, 0.37037037037037035, 0.4094488188976378, 0.4094488188976378, 0.4126984126984127]</t>
-  </si>
-  <si>
-    <t>[0.4528301886792453, 0.45627376425855515, 0.4528301886792453, 0.36445108289768485, 0.3694362017804154, 0.3724756918474196, 0.42276422764227645, 0.41935483870967744, 0.4094488188976378]</t>
-  </si>
-  <si>
-    <t>[0.4528301886792453, 0.45627376425855515, 0.4580152671755725, 0.36459114778694673, 0.3741648106904232, 0.37351190476190477, 0.41935483870967744, 0.4262295081967213, 0.4132231404958678]</t>
-  </si>
-  <si>
-    <t>[0.7874015748031497, 0.7377049180327869, 0.6610169491525424, 0.7588785046728972, 0.7431906614785992, 0.752851711026616, 0.8148148148148148, 0.8275862068965517, 0.8214285714285714]</t>
-  </si>
-  <si>
-    <t>[0.7131782945736435, 0.752, 0.6929133858267716, 0.7970749542961609, 0.7692307692307693, 0.7883211678832117, 0.8363636363636363, 0.8070175438596491, 0.8363636363636363]</t>
-  </si>
-  <si>
-    <t>[0.6222222222222222, 0.6551724137931034, 0.6549707602339181, 0.7576687116564417, 0.7654320987654321, 0.7376543209876543, 0.7246376811594203, 0.7352941176470589, 0.7536231884057971]</t>
-  </si>
-  <si>
-    <t>[0.4791666666666667, 0.40816326530612246, 0.4752475247524752, 0.27311522048364156, 0.2627118644067797, 0.2664714494875549, 0.2, 0.21428571428571427, 0.2641509433962264]</t>
-  </si>
-  <si>
-    <t>[0.4919786096256685, 0.4270833333333333, 0.49473684210526314, 0.29190751445086704, 0.25178826895565093, 0.24495677233429394, 0.19230769230769232, 0.23728813559322035, 0.27586206896551724]</t>
-  </si>
-  <si>
-    <t>[0.3783783783783784, 0.37209302325581395, 0.3969465648854962, 0.25316455696202533, 0.24868913857677902, 0.25018839487565936, 0.21311475409836064, 0.19672131147540983, 0.21138211382113822]</t>
-  </si>
-  <si>
-    <t>[0.3735408560311284, 0.34782608695652173, 0.39846743295019155, 0.24962630792227206, 0.2646239554317549, 0.24393939393939393, 0.21138211382113822, 0.2, 0.22580645161290322]</t>
-  </si>
-  <si>
-    <t>[0.13513513513513514, 0.23684210526315788, 0.275, 0.14074074074074075, 0.15053763440860216, 0.13333333333333333, 0.18181818181818182, 0.37037037037037035, 0.23076923076923078]</t>
-  </si>
-  <si>
-    <t>[0.25316455696202533, 0.23376623376623376, 0.3132530120481928, 0.15384615384615385, 0.14545454545454545, 0.16, 0.25, 0.3076923076923077, 0.2962962962962963]</t>
-  </si>
-  <si>
-    <t>[0.589041095890411, 0.5394736842105263, 0.5616438356164384, 0.5240384615384616, 0.4439140811455847, 0.47393364928909953, 0.20512820512820512, 0.32653061224489793, 0.358974358974359]</t>
+    <t>Mechanistic_Lit</t>
   </si>
 </sst>
 </file>
@@ -473,10 +422,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,440 +453,332 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0.4109662716662562</v>
+        <v>0.3970767048424191</v>
       </c>
       <c r="E2">
-        <v>0.03685981552856901</v>
+        <v>0.03789923547425617</v>
       </c>
       <c r="F2">
-        <v>0.3809146269595289</v>
+        <v>0.3661776256474571</v>
       </c>
       <c r="G2">
-        <v>0.4410179163729835</v>
+        <v>0.4279757840373811</v>
       </c>
       <c r="H2">
-        <v>0.3636363636363636</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.4562737642585551</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>9</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>0.01852524280548096</v>
       </c>
       <c r="D3">
-        <v>0.4108595644683798</v>
+        <v>0.3979399190158348</v>
       </c>
       <c r="E3">
-        <v>0.03514276490667372</v>
+        <v>0.03795133788761185</v>
       </c>
       <c r="F3">
-        <v>0.3822078235455624</v>
+        <v>0.3669983609535189</v>
       </c>
       <c r="G3">
-        <v>0.4395113053911973</v>
+        <v>0.4288814770781507</v>
       </c>
       <c r="H3">
-        <v>0.3630952380952381</v>
+        <v>0.0008632141734157273</v>
       </c>
       <c r="I3">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="J3">
-        <v>-0.0001067071978763656</v>
-      </c>
-      <c r="K3">
-        <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>0.316013514995575</v>
       </c>
       <c r="D4">
-        <v>0.4133183337102397</v>
+        <v>0.4000205638873466</v>
       </c>
       <c r="E4">
-        <v>0.03510294531558621</v>
+        <v>0.03693785699617597</v>
       </c>
       <c r="F4">
-        <v>0.3846990575240621</v>
+        <v>0.3699052923169661</v>
       </c>
       <c r="G4">
-        <v>0.4419376098964173</v>
+        <v>0.430135835457727</v>
       </c>
       <c r="H4">
-        <v>0.3644510828976849</v>
+        <v>0.002943859044927499</v>
       </c>
       <c r="I4">
-        <v>0.4562737642585551</v>
-      </c>
-      <c r="J4">
-        <v>0.002352062043983472</v>
-      </c>
-      <c r="K4">
-        <v>9</v>
-      </c>
-      <c r="L4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>0.3095563054084778</v>
       </c>
       <c r="D5">
-        <v>0.4153549523061015</v>
+        <v>0.4006527919316857</v>
       </c>
       <c r="E5">
-        <v>0.03505848589556244</v>
+        <v>0.03779482208503797</v>
       </c>
       <c r="F5">
-        <v>0.3867719236885908</v>
+        <v>0.3698388405115217</v>
       </c>
       <c r="G5">
-        <v>0.4439379809236123</v>
+        <v>0.4314667433518497</v>
       </c>
       <c r="H5">
-        <v>0.3645911477869467</v>
+        <v>0.0035760870892666</v>
       </c>
       <c r="I5">
-        <v>0.4580152671755725</v>
-      </c>
-      <c r="J5">
-        <v>0.004388680639845322</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.7672082124785032</v>
+        <v>0.7638708958252454</v>
       </c>
       <c r="E6">
-        <v>0.04973136134898992</v>
+        <v>0.04927418756585918</v>
       </c>
       <c r="F6">
-        <v>0.7266624533473062</v>
+        <v>0.7236978684590574</v>
       </c>
       <c r="G6">
-        <v>0.8077539716097003</v>
+        <v>0.8040439231914334</v>
       </c>
       <c r="H6">
-        <v>0.6610169491525424</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.8275862068965517</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>0.01212781667709351</v>
       </c>
       <c r="D7">
-        <v>0.7769403764886087</v>
+        <v>0.7755464453547009</v>
       </c>
       <c r="E7">
-        <v>0.04750369100858307</v>
+        <v>0.0497233457030224</v>
       </c>
       <c r="F7">
-        <v>0.7382108271412542</v>
+        <v>0.7350072213442377</v>
       </c>
       <c r="G7">
-        <v>0.8156699258359632</v>
+        <v>0.816085669365164</v>
       </c>
       <c r="H7">
-        <v>0.6929133858267716</v>
+        <v>0.01167554952945549</v>
       </c>
       <c r="I7">
-        <v>0.8363636363636363</v>
-      </c>
-      <c r="J7">
-        <v>0.00973216401010546</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>0.1838713884353638</v>
       </c>
       <c r="D8">
-        <v>0.7118528349856719</v>
+        <v>0.7171313936862913</v>
       </c>
       <c r="E8">
-        <v>0.05008342430443757</v>
+        <v>0.04211294041656464</v>
       </c>
       <c r="F8">
-        <v>0.6710200404827619</v>
+        <v>0.6827968994733923</v>
       </c>
       <c r="G8">
-        <v>0.7526856294885819</v>
+        <v>0.7514658878991903</v>
       </c>
       <c r="H8">
-        <v>0.6222222222222222</v>
+        <v>-0.04673950213895406</v>
       </c>
       <c r="I8">
-        <v>0.7654320987654321</v>
-      </c>
-      <c r="J8">
-        <v>-0.05535537749283137</v>
-      </c>
-      <c r="K8">
-        <v>9</v>
-      </c>
-      <c r="L8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.3159236276427979</v>
+        <v>0.298768178285252</v>
       </c>
       <c r="E9">
-        <v>0.1022519099752372</v>
+        <v>0.08255449068852259</v>
       </c>
       <c r="F9">
-        <v>0.2325580973194454</v>
+        <v>0.2314618668580167</v>
       </c>
       <c r="G9">
-        <v>0.3992891579661504</v>
+        <v>0.3660744897124874</v>
       </c>
       <c r="H9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.4791666666666667</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>9</v>
-      </c>
-      <c r="L9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
       </c>
       <c r="C10">
         <v>0.01852524280548096</v>
       </c>
       <c r="D10">
-        <v>0.3231010264079452</v>
+        <v>0.2972835491487772</v>
       </c>
       <c r="E10">
-        <v>0.1093710037140403</v>
+        <v>0.08880866981132686</v>
       </c>
       <c r="F10">
-        <v>0.2339313304205899</v>
+        <v>0.2248782331216661</v>
       </c>
       <c r="G10">
-        <v>0.4122707223953005</v>
+        <v>0.3696888651758883</v>
       </c>
       <c r="H10">
-        <v>0.1923076923076923</v>
+        <v>-0.001484629136474847</v>
       </c>
       <c r="I10">
-        <v>0.4947368421052631</v>
-      </c>
-      <c r="J10">
-        <v>0.007177398765147336</v>
-      </c>
-      <c r="K10">
-        <v>9</v>
-      </c>
-      <c r="L10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C11">
         <v>0.316013514995575</v>
       </c>
       <c r="D11">
-        <v>0.2800753595921179</v>
+        <v>0.2797979806542273</v>
       </c>
       <c r="E11">
-        <v>0.07493887244000315</v>
+        <v>0.07574977294347855</v>
       </c>
       <c r="F11">
-        <v>0.218978028067378</v>
+        <v>0.2180395255325975</v>
       </c>
       <c r="G11">
-        <v>0.3411726911168578</v>
+        <v>0.3415564357758572</v>
       </c>
       <c r="H11">
-        <v>0.1967213114754098</v>
+        <v>-0.0189701976310247</v>
       </c>
       <c r="I11">
-        <v>0.3969465648854962</v>
-      </c>
-      <c r="J11">
-        <v>-0.03584826805068003</v>
-      </c>
-      <c r="K11">
-        <v>9</v>
-      </c>
-      <c r="L11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C12">
         <v>0.3095563054084778</v>
       </c>
       <c r="D12">
-        <v>0.2794680665183671</v>
+        <v>0.2665124406124561</v>
       </c>
       <c r="E12">
-        <v>0.06983071763320324</v>
+        <v>0.07434509154205102</v>
       </c>
       <c r="F12">
-        <v>0.2225353910332629</v>
+        <v>0.2058992160297347</v>
       </c>
       <c r="G12">
-        <v>0.3364007420034713</v>
+        <v>0.3271256651951776</v>
       </c>
       <c r="H12">
-        <v>0.2</v>
+        <v>-0.03225573767279594</v>
       </c>
       <c r="I12">
-        <v>0.3984674329501915</v>
-      </c>
-      <c r="J12">
-        <v>-0.03645556112443082</v>
-      </c>
-      <c r="K12">
-        <v>9</v>
-      </c>
-      <c r="L12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -946,7 +787,7 @@
         <v>0.2060607479820836</v>
       </c>
       <c r="E13">
-        <v>0.07569325117149517</v>
+        <v>0.07569325117149518</v>
       </c>
       <c r="F13">
         <v>0.1443483748113664</v>
@@ -955,27 +796,18 @@
         <v>0.2677731211528008</v>
       </c>
       <c r="H13">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0.3703703703703703</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>9</v>
-      </c>
-      <c r="L13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <v>0.01212781667709351</v>
@@ -993,57 +825,39 @@
         <v>0.2863586962824998</v>
       </c>
       <c r="H14">
-        <v>0.1454545454545454</v>
+        <v>0.02876959713633365</v>
       </c>
       <c r="I14">
-        <v>0.3132530120481928</v>
-      </c>
-      <c r="J14">
-        <v>0.02876959713633365</v>
-      </c>
-      <c r="K14">
-        <v>9</v>
-      </c>
-      <c r="L14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
         <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
       </c>
       <c r="C15">
         <v>0.1838713884353638</v>
       </c>
       <c r="D15">
-        <v>0.4469642204486648</v>
+        <v>0.4471045252576443</v>
       </c>
       <c r="E15">
-        <v>0.11986264066768</v>
+        <v>0.1199534821699289</v>
       </c>
       <c r="F15">
-        <v>0.3492407392184513</v>
+        <v>0.3493069813521009</v>
       </c>
       <c r="G15">
-        <v>0.5446877016788783</v>
+        <v>0.5449020691631876</v>
       </c>
       <c r="H15">
-        <v>0.2051282051282051</v>
+        <v>0.2410437772755607</v>
       </c>
       <c r="I15">
-        <v>0.589041095890411</v>
-      </c>
-      <c r="J15">
-        <v>0.2409034724665812</v>
-      </c>
-      <c r="K15">
-        <v>9</v>
-      </c>
-      <c r="L15" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
